--- a/통합댓글정리.xlsx
+++ b/통합댓글정리.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주제별 묶음" sheetId="1" r:id="Rc1b48b613efe4317"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체댓글" sheetId="2" r:id="R1d6d8eeb51f141eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주제별 묶음" sheetId="1" r:id="Rb1a6339c6900473f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체댓글" sheetId="2" r:id="Rb3008daec7d1477e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -97,7 +97,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -157,6 +157,9 @@
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -165,21 +168,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TopicGroups" displayName="TopicGroups" ref="A7:F34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="6">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TopicGroups" displayName="TopicGroups" ref="A7:G36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="7">
     <x:tableColumn id="1" name="주제"/>
     <x:tableColumn id="2" name="대표 질문·내용"/>
     <x:tableColumn id="3" name="댓글 수"/>
     <x:tableColumn id="4" name="인스타그램"/>
     <x:tableColumn id="5" name="유튜브"/>
-    <x:tableColumn id="6" name="통합 댓글 ID"/>
+    <x:tableColumn id="6" name="X"/>
+    <x:tableColumn id="7" name="통합 댓글 ID"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AllComments" displayName="AllComments" ref="A7:M69" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AllComments" displayName="AllComments" ref="A7:M75" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="통합 ID"/>
     <x:tableColumn id="2" name="플랫폼"/>
@@ -399,18 +403,20 @@
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="64" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="64" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>인스타그램·유튜브 통합 댓글 정리</x:v>
+        <x:v>인스타그램·유튜브·X 통합 댓글 정리</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
       <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="4"/>
@@ -419,16 +425,18 @@
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
       <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="4" t="str">
-        <x:v>직접 댓글 62개 · 인스타그램 51개 + 유튜브 11개 · 개별 캡처 62장 · 27개 주제</x:v>
+        <x:v>직접 댓글 68개 · 인스타그램 51개 + 유튜브 11개 + X 6개 · 개별 캡처 68장 · 29개 주제</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
       <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="4" t="str">
@@ -439,14 +447,16 @@
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
       <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="2"/>
+      <x:c r="A6" s="4"/>
       <x:c r="B6" s="2"/>
       <x:c r="C6" s="2"/>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2"/>
+      <x:c r="G6" s="2"/>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" s="8" t="str">
@@ -465,6 +475,9 @@
         <x:v>유튜브</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
         <x:v>통합 댓글 ID</x:v>
       </x:c>
     </x:row>
@@ -487,7 +500,11 @@
         <x:f>COUNT('전체댓글'!L59,'전체댓글'!L60,'전체댓글'!L61)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="str">
+      <x:c r="F8" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="str">
         <x:v>IG025, IG031, IG033, IG037, IG045, IG053, IG063, IG067, IG079, IG081, YT001, YT002, YT003</x:v>
       </x:c>
     </x:row>
@@ -510,7 +527,11 @@
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F9" s="9" t="str">
+      <x:c r="F9" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="9" t="str">
         <x:v>IG025, IG033, IG071, IG095, IG103</x:v>
       </x:c>
     </x:row>
@@ -533,54 +554,66 @@
         <x:f>COUNT('전체댓글'!L64,'전체댓글'!L68)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F10" s="9" t="str">
+      <x:c r="F10" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="9" t="str">
         <x:v>IG059, IG077, IG097, YT006, YT010</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
       <x:c r="A11" s="9" t="str">
+        <x:v>일상·운동·장난 질문</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>세탁·운동 등 가벼운 일상 질문과 장난 섞인 대화</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L9,'전체댓글'!L25,'전체댓글'!L49,'전체댓글'!L62,'전체댓글'!L73)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L9,'전체댓글'!L25,'전체댓글'!L49)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L62)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L73)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="9" t="str">
+        <x:v>IG003, IG041, IG089, YT004, X004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="48" customHeight="1">
+      <x:c r="A12" s="9" t="str">
         <x:v>출시·공개·얼리액세스</x:v>
       </x:c>
-      <x:c r="B11" s="10" t="str">
+      <x:c r="B12" s="10" t="str">
         <x:v>게임 공개·출시 일정과 얼리액세스 계획은 어떻게 되나요?</x:v>
       </x:c>
-      <x:c r="C11" s="13" t="n">
+      <x:c r="C12" s="13" t="n">
         <x:f>COUNT('전체댓글'!L28,'전체댓글'!L52,'전체댓글'!L54,'전체댓글'!L56)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D11" s="13" t="n">
+      <x:c r="D12" s="13" t="n">
         <x:f>COUNT('전체댓글'!L28,'전체댓글'!L52,'전체댓글'!L54,'전체댓글'!L56)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E11" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" s="9" t="str">
+      <x:c r="E12" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="9" t="str">
         <x:v>IG047, IG095, IG099, IG103</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="9" t="str">
-        <x:v>일상·운동·장난 질문</x:v>
-      </x:c>
-      <x:c r="B12" s="10" t="str">
-        <x:v>세탁·운동 등 가벼운 일상 질문과 장난 섞인 대화</x:v>
-      </x:c>
-      <x:c r="C12" s="13" t="n">
-        <x:f>COUNT('전체댓글'!L9,'전체댓글'!L25,'전체댓글'!L49,'전체댓글'!L62)</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="13" t="n">
-        <x:f>COUNT('전체댓글'!L9,'전체댓글'!L25,'전체댓글'!L49)</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E12" s="13" t="n">
-        <x:f>COUNT('전체댓글'!L62)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F12" s="9" t="str">
-        <x:v>IG003, IG041, IG089, YT004</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
@@ -602,7 +635,11 @@
         <x:f>COUNT('전체댓글'!L66)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F13" s="9" t="str">
+      <x:c r="F13" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="9" t="str">
         <x:v>IG012, IG085, IG093, YT008</x:v>
       </x:c>
     </x:row>
@@ -614,8 +651,8 @@
         <x:v>응원, 재미있다는 반응, 영상 시청 후기</x:v>
       </x:c>
       <x:c r="C14" s="13" t="n">
-        <x:f>COUNT('전체댓글'!L32,'전체댓글'!L46,'전체댓글'!L58)</x:f>
-        <x:v>3</x:v>
+        <x:f>COUNT('전체댓글'!L32,'전체댓글'!L46,'전체댓글'!L58,'전체댓글'!L70)</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D14" s="13" t="n">
         <x:f>COUNT('전체댓글'!L32,'전체댓글'!L46,'전체댓글'!L58)</x:f>
@@ -625,192 +662,228 @@
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="9" t="str">
-        <x:v>IG055, IG083, IG106</x:v>
+      <x:c r="F14" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L70)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="9" t="str">
+        <x:v>IG055, IG083, IG106, X001</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
       <x:c r="A15" s="9" t="str">
+        <x:v>좋아하는 게임·주력 장르</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>가장 좋아하는 게임과 주로 플레이하는 게임 장르는 무엇인가요?</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L15,'전체댓글'!L29,'전체댓글'!L57,'전체댓글'!L72)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L15,'전체댓글'!L29,'전체댓글'!L57)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L72)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="9" t="str">
+        <x:v>IG021, IG049, IG105, X003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="48" customHeight="1">
+      <x:c r="A16" s="9" t="str">
         <x:v>팀원·음악 인력 모집</x:v>
       </x:c>
-      <x:c r="B15" s="10" t="str">
+      <x:c r="B16" s="10" t="str">
         <x:v>음악 담당이나 추가 팀원을 모집할 계획이 있나요?</x:v>
       </x:c>
-      <x:c r="C15" s="13" t="n">
+      <x:c r="C16" s="13" t="n">
         <x:f>COUNT('전체댓글'!L19,'전체댓글'!L48,'전체댓글'!L50)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D15" s="13" t="n">
+      <x:c r="D16" s="13" t="n">
         <x:f>COUNT('전체댓글'!L19,'전체댓글'!L48,'전체댓글'!L50)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E15" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="9" t="str">
+      <x:c r="E16" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="9" t="str">
         <x:v>IG029, IG087, IG091</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="48" customHeight="1">
-      <x:c r="A16" s="9" t="str">
-        <x:v>좋아하는 게임</x:v>
-      </x:c>
-      <x:c r="B16" s="10" t="str">
-        <x:v>가장 재미있게 했거나 좋아하는 게임, 하나만 보존할 게임은 무엇인가요?</x:v>
-      </x:c>
-      <x:c r="C16" s="13" t="n">
-        <x:f>COUNT('전체댓글'!L15,'전체댓글'!L29,'전체댓글'!L57)</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D16" s="13" t="n">
-        <x:f>COUNT('전체댓글'!L15,'전체댓글'!L29,'전체댓글'!L57)</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F16" s="9" t="str">
-        <x:v>IG021, IG049, IG105</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" s="9" t="str">
+        <x:v>업무 고충·직업병·탈주</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>일하면서 겪는 고충·직업병과 그만두고 싶었던 순간은 무엇인가요?</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L16,'전체댓글'!L69,'전체댓글'!L74)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L16)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L69)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L74)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="9" t="str">
+        <x:v>IG023, YT011, X005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="48" customHeight="1">
+      <x:c r="A18" s="9" t="str">
         <x:v>근무시간·수면·개발 우선순위</x:v>
       </x:c>
-      <x:c r="B17" s="10" t="str">
+      <x:c r="B18" s="10" t="str">
         <x:v>게임 개발·영상 제작·수면 시간을 어떻게 나누고, 무엇을 우선하나요?</x:v>
       </x:c>
-      <x:c r="C17" s="13" t="n">
+      <x:c r="C18" s="13" t="n">
         <x:f>COUNT('전체댓글'!L12,'전체댓글'!L30)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D17" s="13" t="n">
+      <x:c r="D18" s="13" t="n">
         <x:f>COUNT('전체댓글'!L12,'전체댓글'!L30)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E17" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" s="9" t="str">
+      <x:c r="E18" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" s="9" t="str">
         <x:v>IG012, IG051</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="48" customHeight="1">
-      <x:c r="A18" s="9" t="str">
+    <x:row r="19" ht="48" customHeight="1">
+      <x:c r="A19" s="9" t="str">
         <x:v>개발 기술·엔진·구현</x:v>
       </x:c>
-      <x:c r="B18" s="10" t="str">
+      <x:c r="B19" s="10" t="str">
         <x:v>사용하는 게임 엔진·언어·기술 스택과 주요 시스템 구현 방법은 무엇인가요?</x:v>
       </x:c>
-      <x:c r="C18" s="13" t="n">
+      <x:c r="C19" s="13" t="n">
         <x:f>COUNT('전체댓글'!L11,'전체댓글'!L42)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D18" s="13" t="n">
+      <x:c r="D19" s="13" t="n">
         <x:f>COUNT('전체댓글'!L11,'전체댓글'!L42)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E18" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F18" s="9" t="str">
+      <x:c r="E19" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="9" t="str">
         <x:v>IG009, IG075</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="48" customHeight="1">
-      <x:c r="A19" s="9" t="str">
+    <x:row r="20" ht="48" customHeight="1">
+      <x:c r="A20" s="9" t="str">
         <x:v>협업·의견 충돌 해결</x:v>
       </x:c>
-      <x:c r="B19" s="10" t="str">
+      <x:c r="B20" s="10" t="str">
         <x:v>개발자와 아티스트의 의견이 다를 때 어떻게 이해하고 조율하나요?</x:v>
       </x:c>
-      <x:c r="C19" s="13" t="n">
+      <x:c r="C20" s="13" t="n">
         <x:f>COUNT('전체댓글'!L14,'전체댓글'!L55)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D19" s="13" t="n">
+      <x:c r="D20" s="13" t="n">
         <x:f>COUNT('전체댓글'!L14,'전체댓글'!L55)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E19" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F19" s="9" t="str">
+      <x:c r="E20" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="9" t="str">
         <x:v>IG018, IG101</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="48" customHeight="1">
-      <x:c r="A20" s="9" t="str">
+    <x:row r="21" ht="48" customHeight="1">
+      <x:c r="A21" s="9" t="str">
         <x:v>MBTI</x:v>
       </x:c>
-      <x:c r="B20" s="10" t="str">
+      <x:c r="B21" s="10" t="str">
         <x:v>개발자와 아티스트의 MBTI는 무엇인가요?</x:v>
       </x:c>
-      <x:c r="C20" s="13" t="n">
+      <x:c r="C21" s="13" t="n">
         <x:f>COUNT('전체댓글'!L10,'전체댓글'!L26)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D20" s="13" t="n">
+      <x:c r="D21" s="13" t="n">
         <x:f>COUNT('전체댓글'!L10,'전체댓글'!L26)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E20" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F20" s="9" t="str">
+      <x:c r="E21" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="9" t="str">
         <x:v>IG006, IG043</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="48" customHeight="1">
-      <x:c r="A21" s="9" t="str">
+    <x:row r="22" ht="48" customHeight="1">
+      <x:c r="A22" s="9" t="str">
         <x:v>홍보·SNS 운영</x:v>
       </x:c>
-      <x:c r="B21" s="10" t="str">
+      <x:c r="B22" s="10" t="str">
         <x:v>릴스 홍보를 시작한 계기와 인스타그램 답글 담당자는 누구인가요?</x:v>
       </x:c>
-      <x:c r="C21" s="13" t="n">
+      <x:c r="C22" s="13" t="n">
         <x:f>COUNT('전체댓글'!L22,'전체댓글'!L37)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D21" s="13" t="n">
+      <x:c r="D22" s="13" t="n">
         <x:f>COUNT('전체댓글'!L22,'전체댓글'!L37)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E21" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F21" s="9" t="str">
+      <x:c r="E22" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G22" s="9" t="str">
         <x:v>IG035, IG065</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="48" customHeight="1">
-      <x:c r="A22" s="9" t="str">
-        <x:v>업무 고충·직업병·탈주</x:v>
-      </x:c>
-      <x:c r="B22" s="10" t="str">
-        <x:v>일하면서 겪는 고충·직업병과 그만두고 싶었던 순간은 무엇인가요?</x:v>
-      </x:c>
-      <x:c r="C22" s="13" t="n">
-        <x:f>COUNT('전체댓글'!L16,'전체댓글'!L69)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="13" t="n">
-        <x:f>COUNT('전체댓글'!L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E22" s="13" t="n">
-        <x:f>COUNT('전체댓글'!L69)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F22" s="9" t="str">
-        <x:v>IG023, YT011</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -832,246 +905,290 @@
         <x:f>COUNT('전체댓글'!L63,'전체댓글'!L65)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F23" s="9" t="str">
+      <x:c r="F23" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" s="9" t="str">
         <x:v>YT005, YT007</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
       <x:c r="A24" s="9" t="str">
+        <x:v>게임 기획·개발 범위 조절</x:v>
+      </x:c>
+      <x:c r="B24" s="10" t="str">
+        <x:v>개발 과정에서 제외한 기능·스토리·디테일과 아쉬웠던 점은 무엇인가요?</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L74,'전체댓글'!L75)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L74,'전체댓글'!L75)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G24" s="9" t="str">
+        <x:v>X005, X006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="48" customHeight="1">
+      <x:c r="A25" s="9" t="str">
         <x:v>게임 철학·좋은 게임의 기준</x:v>
       </x:c>
-      <x:c r="B24" s="10" t="str">
+      <x:c r="B25" s="10" t="str">
         <x:v>좋은 게임의 기준을 어떻게 생각하나요?</x:v>
       </x:c>
-      <x:c r="C24" s="13" t="n">
+      <x:c r="C25" s="13" t="n">
         <x:f>COUNT('전체댓글'!L41)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D24" s="13" t="n">
+      <x:c r="D25" s="13" t="n">
         <x:f>COUNT('전체댓글'!L41)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E24" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F24" s="9" t="str">
+      <x:c r="E25" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F25" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G25" s="9" t="str">
         <x:v>IG073</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="48" customHeight="1">
-      <x:c r="A25" s="9" t="str">
+    <x:row r="26" ht="48" customHeight="1">
+      <x:c r="A26" s="9" t="str">
         <x:v>다른 게임 플레이·소감</x:v>
       </x:c>
-      <x:c r="B25" s="10" t="str">
+      <x:c r="B26" s="10" t="str">
         <x:v>갈바테인을 플레이해 보셨나요? 소감은 어떤가요?</x:v>
       </x:c>
-      <x:c r="C25" s="13" t="n">
+      <x:c r="C26" s="13" t="n">
         <x:f>COUNT('전체댓글'!L18)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D25" s="13" t="n">
+      <x:c r="D26" s="13" t="n">
         <x:f>COUNT('전체댓글'!L18)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E25" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F25" s="9" t="str">
+      <x:c r="E26" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G26" s="9" t="str">
         <x:v>IG027</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="48" customHeight="1">
-      <x:c r="A26" s="9" t="str">
+    <x:row r="27" ht="48" customHeight="1">
+      <x:c r="A27" s="9" t="str">
         <x:v>좋아하는 애니메이션</x:v>
       </x:c>
-      <x:c r="B26" s="10" t="str">
+      <x:c r="B27" s="10" t="str">
         <x:v>가장 좋아하는 애니메이션은 무엇인가요?</x:v>
       </x:c>
-      <x:c r="C26" s="13" t="n">
+      <x:c r="C27" s="13" t="n">
         <x:f>COUNT('전체댓글'!L33)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D26" s="13" t="n">
+      <x:c r="D27" s="13" t="n">
         <x:f>COUNT('전체댓글'!L33)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E26" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F26" s="9" t="str">
+      <x:c r="E27" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F27" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G27" s="9" t="str">
         <x:v>IG057</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="48" customHeight="1">
-      <x:c r="A27" s="9" t="str">
+    <x:row r="28" ht="48" customHeight="1">
+      <x:c r="A28" s="9" t="str">
         <x:v>게임 캐릭터 더빙</x:v>
       </x:c>
-      <x:c r="B27" s="10" t="str">
+      <x:c r="B28" s="10" t="str">
         <x:v>게임 캐릭터 더빙도 직접 하시나요?</x:v>
       </x:c>
-      <x:c r="C27" s="13" t="n">
+      <x:c r="C28" s="13" t="n">
         <x:f>COUNT('전체댓글'!L13)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D27" s="13" t="n">
+      <x:c r="D28" s="13" t="n">
         <x:f>COUNT('전체댓글'!L13)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E27" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F27" s="9" t="str">
+      <x:c r="E28" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F28" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G28" s="9" t="str">
         <x:v>IG015</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="48" customHeight="1">
-      <x:c r="A28" s="9" t="str">
+    <x:row r="29" ht="48" customHeight="1">
+      <x:c r="A29" s="9" t="str">
         <x:v>개발 장소</x:v>
       </x:c>
-      <x:c r="B28" s="10" t="str">
+      <x:c r="B29" s="10" t="str">
         <x:v>게임 개발은 어디에서 하나요?</x:v>
       </x:c>
-      <x:c r="C28" s="13" t="n">
+      <x:c r="C29" s="13" t="n">
         <x:f>COUNT('전체댓글'!L35)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D28" s="13" t="n">
+      <x:c r="D29" s="13" t="n">
         <x:f>COUNT('전체댓글'!L35)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E28" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F28" s="9" t="str">
+      <x:c r="E29" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F29" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="9" t="str">
         <x:v>IG061</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="48" customHeight="1">
-      <x:c r="A29" s="9" t="str">
+    <x:row r="30" ht="48" customHeight="1">
+      <x:c r="A30" s="9" t="str">
         <x:v>디스코드 사용</x:v>
       </x:c>
-      <x:c r="B29" s="10" t="str">
+      <x:c r="B30" s="10" t="str">
         <x:v>평소 디스코드를 얼마나 사용하나요?</x:v>
       </x:c>
-      <x:c r="C29" s="13" t="n">
+      <x:c r="C30" s="13" t="n">
         <x:f>COUNT('전체댓글'!L24)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D29" s="13" t="n">
+      <x:c r="D30" s="13" t="n">
         <x:f>COUNT('전체댓글'!L24)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E29" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F29" s="9" t="str">
+      <x:c r="E30" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F30" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G30" s="9" t="str">
         <x:v>IG039</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="48" customHeight="1">
-      <x:c r="A30" s="9" t="str">
+    <x:row r="31" ht="48" customHeight="1">
+      <x:c r="A31" s="9" t="str">
         <x:v>이스터에그</x:v>
       </x:c>
-      <x:c r="B30" s="10" t="str">
+      <x:c r="B31" s="10" t="str">
         <x:v>게임에 이스터에그가 숨겨져 있나요?</x:v>
       </x:c>
-      <x:c r="C30" s="13" t="n">
+      <x:c r="C31" s="13" t="n">
         <x:f>COUNT('전체댓글'!L39)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D30" s="13" t="n">
+      <x:c r="D31" s="13" t="n">
         <x:f>COUNT('전체댓글'!L39)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E30" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F30" s="9" t="str">
+      <x:c r="E31" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F31" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G31" s="9" t="str">
         <x:v>IG069</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="48" customHeight="1">
-      <x:c r="A31" s="9" t="str">
+    <x:row r="32" ht="48" customHeight="1">
+      <x:c r="A32" s="9" t="str">
         <x:v>Q&amp;A 답변 제작 안내</x:v>
       </x:c>
-      <x:c r="B31" s="10" t="str">
+      <x:c r="B32" s="10" t="str">
         <x:v>Q&amp;A 답변 영상 제작에 대한 게시자 안내</x:v>
       </x:c>
-      <x:c r="C31" s="13" t="n">
+      <x:c r="C32" s="13" t="n">
         <x:f>COUNT('전체댓글'!L8)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D31" s="13" t="n">
+      <x:c r="D32" s="13" t="n">
         <x:f>COUNT('전체댓글'!L8)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E31" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F31" s="9" t="str">
+      <x:c r="E32" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F32" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="9" t="str">
         <x:v>IG001</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="48" customHeight="1">
-      <x:c r="A32" s="9" t="str">
+    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="A33" s="9" t="str">
         <x:v>출시 플랫폼</x:v>
       </x:c>
-      <x:c r="B32" s="10" t="str">
+      <x:c r="B33" s="10" t="str">
         <x:v>게임을 어떤 플랫폼으로 출시할 예정인가요?</x:v>
       </x:c>
-      <x:c r="C32" s="13" t="n">
+      <x:c r="C33" s="13" t="n">
         <x:f>COUNT('전체댓글'!L63)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D32" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E32" s="13" t="n">
+      <x:c r="D33" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E33" s="13" t="n">
         <x:f>COUNT('전체댓글'!L63)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F32" s="9" t="str">
+      <x:c r="F33" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G33" s="9" t="str">
         <x:v>YT005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="48" customHeight="1">
-      <x:c r="A33" s="9" t="str">
-        <x:v>AI 도구·요금제·작업 방식</x:v>
-      </x:c>
-      <x:c r="B33" s="10" t="str">
-        <x:v>어떤 AI와 요금제를 사용하고, 어떤 작업·워크플로우에 활용하나요?</x:v>
-      </x:c>
-      <x:c r="C33" s="13" t="n">
-        <x:f>COUNT('전체댓글'!L67)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D33" s="13" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E33" s="13" t="n">
-        <x:f>COUNT('전체댓글'!L67)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F33" s="9" t="str">
-        <x:v>YT009</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="48" customHeight="1">
       <x:c r="A34" s="9" t="str">
-        <x:v>공모전 참여</x:v>
+        <x:v>AI 도구·요금제·작업 방식</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>공모전에 참여할 의향이 있나요?</x:v>
+        <x:v>어떤 AI와 요금제를 사용하고, 어떤 작업·워크플로우에 활용하나요?</x:v>
       </x:c>
       <x:c r="C34" s="13" t="n">
         <x:f>COUNT('전체댓글'!L67)</x:f>
@@ -1085,59 +1202,124 @@
         <x:f>COUNT('전체댓글'!L67)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F34" s="9" t="str">
+      <x:c r="F34" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G34" s="9" t="str">
         <x:v>YT009</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="2"/>
-      <x:c r="B35" s="2"/>
-      <x:c r="C35" s="14"/>
-      <x:c r="D35" s="14"/>
-      <x:c r="E35" s="14"/>
-      <x:c r="F35" s="2"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="17" t="str">
-        <x:v>전체 댓글 수 (중복 제외)</x:v>
-      </x:c>
-      <x:c r="B36" s="17"/>
-      <x:c r="C36" s="18" t="n">
-        <x:f>COUNTA('전체댓글'!A8:A69)</x:f>
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D36" s="18" t="n">
-        <x:f>COUNTIFS('전체댓글'!B8:B69,"인스타그램")</x:f>
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E36" s="18" t="n">
-        <x:f>COUNTIFS('전체댓글'!B8:B69,"유튜브")</x:f>
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F36" s="17"/>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="9" t="str">
+        <x:v>공모전 참여</x:v>
+      </x:c>
+      <x:c r="B35" s="10" t="str">
+        <x:v>공모전에 참여할 의향이 있나요?</x:v>
+      </x:c>
+      <x:c r="C35" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L67)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D35" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L67)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F35" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G35" s="9" t="str">
+        <x:v>YT009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="48" customHeight="1">
+      <x:c r="A36" s="9" t="str">
+        <x:v>BGM 선정·음악 방향</x:v>
+      </x:c>
+      <x:c r="B36" s="10" t="str">
+        <x:v>게임의 BGM을 어떤 기준으로 선정하고, 음악 방향을 결정하나요?</x:v>
+      </x:c>
+      <x:c r="C36" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L71)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D36" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E36" s="13" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F36" s="13" t="n">
+        <x:f>COUNT('전체댓글'!L71)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G36" s="9" t="str">
+        <x:v>X002</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="2"/>
       <x:c r="B37" s="2"/>
-      <x:c r="C37" s="2"/>
-      <x:c r="D37" s="2"/>
-      <x:c r="E37" s="2"/>
-      <x:c r="F37" s="2"/>
+      <x:c r="C37" s="14"/>
+      <x:c r="D37" s="14"/>
+      <x:c r="E37" s="14"/>
+      <x:c r="F37" s="14"/>
+      <x:c r="G37" s="2"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="2" t="str">
-        <x:v>게시물에 직접 달린 댓글만 포함합니다. IG와 YT 표시로 플랫폼을 구분합니다.</x:v>
-      </x:c>
-      <x:c r="B38" s="2"/>
-      <x:c r="C38" s="2"/>
-      <x:c r="D38" s="2"/>
-      <x:c r="E38" s="2"/>
-      <x:c r="F38" s="2"/>
+      <x:c r="A38" s="17" t="str">
+        <x:v>전체 댓글 수 (중복 제외)</x:v>
+      </x:c>
+      <x:c r="B38" s="17"/>
+      <x:c r="C38" s="18" t="n">
+        <x:f>COUNTA('전체댓글'!A8:A75)</x:f>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D38" s="18" t="n">
+        <x:f>COUNTIFS('전체댓글'!B8:B75,"인스타그램")</x:f>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E38" s="18" t="n">
+        <x:f>COUNTIFS('전체댓글'!B8:B75,"유튜브")</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F38" s="18" t="n">
+        <x:f>COUNTIFS('전체댓글'!B8:B75,"X")</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G38" s="17"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="2"/>
+      <x:c r="B39" s="2"/>
+      <x:c r="C39" s="2"/>
+      <x:c r="D39" s="2"/>
+      <x:c r="E39" s="2"/>
+      <x:c r="F39" s="2"/>
+      <x:c r="G39" s="2"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="2" t="str">
+        <x:v>게시물에 직접 달린 댓글만 포함합니다. X의 MadeInCosmo 작성 댓글과 대댓글은 제외했습니다.</x:v>
+      </x:c>
+      <x:c r="B40" s="2"/>
+      <x:c r="C40" s="2"/>
+      <x:c r="D40" s="2"/>
+      <x:c r="E40" s="2"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f325da9f7914b55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc333cc854e104836"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1148,7 +1330,7 @@
   <x:cols>
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="64" hidden="0" customWidth="1"/>
@@ -1163,7 +1345,7 @@
   <x:sheetData>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>인스타그램·유튜브 직접 댓글 원문과 캡처</x:v>
+        <x:v>인스타그램·유튜브·X 직접 댓글 원문과 캡처</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -1214,7 +1396,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="4" t="str">
-        <x:v>2026-10-08 수집 · IG는 기존 수집 번호, YT는 최신순 번호 · 유튜브 정확한 게시 시각은 화면에 없어 공란</x:v>
+        <x:v>X 출처: https://x.com/MadeInCosmo/status/2102538440730452409</x:v>
       </x:c>
       <x:c r="B5" s="2"/>
       <x:c r="C5" s="2"/>
@@ -1230,7 +1412,9 @@
       <x:c r="M5" s="2"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="2"/>
+      <x:c r="A6" s="4" t="str">
+        <x:v>인스타그램·유튜브: 2026-10-08 수집 / X: 2026-10-11 수집 · 유튜브 정확한 게시 시각은 화면에 없어 공란</x:v>
+      </x:c>
       <x:c r="B6" s="2"/>
       <x:c r="C6" s="2"/>
       <x:c r="D6" s="2"/>
@@ -1600,10 +1784,10 @@
         <x:v>질문</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>좋아하는 게임</x:v>
+        <x:v>좋아하는 게임·주력 장르</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
-        <x:v>좋아하는 게임</x:v>
+        <x:v>좋아하는 게임·주력 장르</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
         <x:v>두 분이 가장 재밌게 플레이 한 게임이 궁금해요</x:v>
@@ -2202,10 +2386,10 @@
         <x:v>질문</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
-        <x:v>좋아하는 게임</x:v>
+        <x:v>좋아하는 게임·주력 장르</x:v>
       </x:c>
       <x:c r="F29" s="10" t="str">
-        <x:v>좋아하는 게임</x:v>
+        <x:v>좋아하는 게임·주력 장르</x:v>
       </x:c>
       <x:c r="G29" s="10" t="str">
         <x:v>두 분이 가장 좋아하는 게임은 뭔가용??</x:v>
@@ -3406,10 +3590,10 @@
         <x:v>질문</x:v>
       </x:c>
       <x:c r="E57" s="9" t="str">
-        <x:v>좋아하는 게임</x:v>
+        <x:v>좋아하는 게임·주력 장르</x:v>
       </x:c>
       <x:c r="F57" s="10" t="str">
-        <x:v>좋아하는 게임</x:v>
+        <x:v>좋아하는 게임·주력 장르</x:v>
       </x:c>
       <x:c r="G57" s="10" t="str">
         <x:v>두분다 지구상에 게임중 단 하나만 보존 할 수 있다면 어떤 게임을?</x:v>
@@ -3929,10 +4113,270 @@
         <x:v>UgyGlaUtMhtlEOSi-Xd4AaABAg</x:v>
       </x:c>
     </x:row>
+    <x:row r="70" ht="61" customHeight="1">
+      <x:c r="A70" s="9" t="str">
+        <x:v>X001</x:v>
+      </x:c>
+      <x:c r="B70" s="21" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C70" s="9" t="str">
+        <x:v>풀뜯는호야 (@Hoya_eat_grass)</x:v>
+      </x:c>
+      <x:c r="D70" s="9" t="str">
+        <x:v>반응·응원</x:v>
+      </x:c>
+      <x:c r="E70" s="9" t="str">
+        <x:v>응원·시청 반응</x:v>
+      </x:c>
+      <x:c r="F70" s="10" t="str">
+        <x:v>응원·시청 반응</x:v>
+      </x:c>
+      <x:c r="G70" s="10" t="str">
+        <x:v>타이밍이 환상적이네요!
+한국은 마침 추석연휴인데
+추석연휴 잘 보내세요~</x:v>
+      </x:c>
+      <x:c r="H70" s="9" t="str">
+        <x:v>Sep 22</x:v>
+      </x:c>
+      <x:c r="I70" s="9" t="d">
+        <x:v>2026-09-22T23:41:15.000Z</x:v>
+      </x:c>
+      <x:c r="J70" s="9" t="e">
+        <x:f>HYPERLINK("captures/x/X001.png","이미지 열기")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=captures/x/X001.png, friendlyName=이미지 열기</x:v>
+      </x:c>
+      <x:c r="K70" s="9" t="e">
+        <x:f>HYPERLINK("https://x.com/Hoya_eat_grass/status/2102543780511662277","원문 열기")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://x.com/Hoya_eat_grass/status/2102543780511662277, friendlyName=원문 열기</x:v>
+      </x:c>
+      <x:c r="L70" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M70" s="9" t="str">
+        <x:v>2102543780511662277</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="48" customHeight="1">
+      <x:c r="A71" s="9" t="str">
+        <x:v>X002</x:v>
+      </x:c>
+      <x:c r="B71" s="21" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C71" s="9" t="str">
+        <x:v>풀뜯는호야 (@Hoya_eat_grass)</x:v>
+      </x:c>
+      <x:c r="D71" s="9" t="str">
+        <x:v>질문</x:v>
+      </x:c>
+      <x:c r="E71" s="9" t="str">
+        <x:v>BGM 선정·음악 방향</x:v>
+      </x:c>
+      <x:c r="F71" s="10" t="str">
+        <x:v>BGM 선정·음악 방향</x:v>
+      </x:c>
+      <x:c r="G71" s="10" t="str">
+        <x:v>BGM같은 경우에는 두분이 갓겜들을 많이하셔서 귀가 높으실텐데 선정하는데 어렵진 않으셨나요</x:v>
+      </x:c>
+      <x:c r="H71" s="9" t="str">
+        <x:v>Sep 22</x:v>
+      </x:c>
+      <x:c r="I71" s="9" t="d">
+        <x:v>2026-09-22T23:40:03.000Z</x:v>
+      </x:c>
+      <x:c r="J71" s="9" t="e">
+        <x:f>HYPERLINK("captures/x/X002.png","이미지 열기")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=captures/x/X002.png, friendlyName=이미지 열기</x:v>
+      </x:c>
+      <x:c r="K71" s="9" t="e">
+        <x:f>HYPERLINK("https://x.com/Hoya_eat_grass/status/2102543480073670659","원문 열기")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://x.com/Hoya_eat_grass/status/2102543480073670659, friendlyName=원문 열기</x:v>
+      </x:c>
+      <x:c r="L71" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M71" s="9" t="str">
+        <x:v>2102543480073670659</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="48" customHeight="1">
+      <x:c r="A72" s="9" t="str">
+        <x:v>X003</x:v>
+      </x:c>
+      <x:c r="B72" s="21" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C72" s="9" t="str">
+        <x:v>풀뜯는호야 (@Hoya_eat_grass)</x:v>
+      </x:c>
+      <x:c r="D72" s="9" t="str">
+        <x:v>질문</x:v>
+      </x:c>
+      <x:c r="E72" s="9" t="str">
+        <x:v>좋아하는 게임·주력 장르</x:v>
+      </x:c>
+      <x:c r="F72" s="10" t="str">
+        <x:v>좋아하는 게임·주력 장르</x:v>
+      </x:c>
+      <x:c r="G72" s="10" t="str">
+        <x:v>두분은 주력 게임장르가 어떻게 되시나요</x:v>
+      </x:c>
+      <x:c r="H72" s="9" t="str">
+        <x:v>Sep 22</x:v>
+      </x:c>
+      <x:c r="I72" s="9" t="d">
+        <x:v>2026-09-22T23:38:53.000Z</x:v>
+      </x:c>
+      <x:c r="J72" s="9" t="e">
+        <x:f>HYPERLINK("captures/x/X003.png","이미지 열기")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=captures/x/X003.png, friendlyName=이미지 열기</x:v>
+      </x:c>
+      <x:c r="K72" s="9" t="e">
+        <x:f>HYPERLINK("https://x.com/Hoya_eat_grass/status/2102543186380157433","원문 열기")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://x.com/Hoya_eat_grass/status/2102543186380157433, friendlyName=원문 열기</x:v>
+      </x:c>
+      <x:c r="L72" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M72" s="9" t="str">
+        <x:v>2102543186380157433</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="48" customHeight="1">
+      <x:c r="A73" s="9" t="str">
+        <x:v>X004</x:v>
+      </x:c>
+      <x:c r="B73" s="21" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C73" s="9" t="str">
+        <x:v>풀뜯는호야 (@Hoya_eat_grass)</x:v>
+      </x:c>
+      <x:c r="D73" s="9" t="str">
+        <x:v>질문</x:v>
+      </x:c>
+      <x:c r="E73" s="9" t="str">
+        <x:v>일상·운동·장난 질문</x:v>
+      </x:c>
+      <x:c r="F73" s="10" t="str">
+        <x:v>일상·운동·장난 질문</x:v>
+      </x:c>
+      <x:c r="G73" s="10" t="str">
+        <x:v>아트팀에 계시는 뉴욕핫걸님께서 본인은 전혀 핫하지 않다고 부정하시는데 어떻게생각하시나요</x:v>
+      </x:c>
+      <x:c r="H73" s="9" t="str">
+        <x:v>Sep 22</x:v>
+      </x:c>
+      <x:c r="I73" s="9" t="d">
+        <x:v>2026-09-22T23:32:51.000Z</x:v>
+      </x:c>
+      <x:c r="J73" s="9" t="e">
+        <x:f>HYPERLINK("captures/x/X004.png","이미지 열기")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=captures/x/X004.png, friendlyName=이미지 열기</x:v>
+      </x:c>
+      <x:c r="K73" s="9" t="e">
+        <x:f>HYPERLINK("https://x.com/Hoya_eat_grass/status/2102541665760334003","원문 열기")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://x.com/Hoya_eat_grass/status/2102541665760334003, friendlyName=원문 열기</x:v>
+      </x:c>
+      <x:c r="L73" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M73" s="9" t="str">
+        <x:v>2102541665760334003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="48" customHeight="1">
+      <x:c r="A74" s="9" t="str">
+        <x:v>X005</x:v>
+      </x:c>
+      <x:c r="B74" s="21" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C74" s="9" t="str">
+        <x:v>풀뜯는호야 (@Hoya_eat_grass)</x:v>
+      </x:c>
+      <x:c r="D74" s="9" t="str">
+        <x:v>질문</x:v>
+      </x:c>
+      <x:c r="E74" s="9" t="str">
+        <x:v>게임 기획·개발 범위 조절</x:v>
+      </x:c>
+      <x:c r="F74" s="10" t="str">
+        <x:v>게임 기획·개발 범위 조절 / 업무 고충·직업병·탈주</x:v>
+      </x:c>
+      <x:c r="G74" s="10" t="str">
+        <x:v>스토리와 디테일 광인이 계시다고 들었는데 직접 만들때 덜어내거나 시간이 없어서 미쳐 인게임내 구현 못하실때 심정이 궁금해요</x:v>
+      </x:c>
+      <x:c r="H74" s="9" t="str">
+        <x:v>Sep 22</x:v>
+      </x:c>
+      <x:c r="I74" s="9" t="d">
+        <x:v>2026-09-22T23:30:47.000Z</x:v>
+      </x:c>
+      <x:c r="J74" s="9" t="e">
+        <x:f>HYPERLINK("captures/x/X005.png","이미지 열기")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=captures/x/X005.png, friendlyName=이미지 열기</x:v>
+      </x:c>
+      <x:c r="K74" s="9" t="e">
+        <x:f>HYPERLINK("https://x.com/Hoya_eat_grass/status/2102541149013708819","원문 열기")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://x.com/Hoya_eat_grass/status/2102541149013708819, friendlyName=원문 열기</x:v>
+      </x:c>
+      <x:c r="L74" s="9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M74" s="9" t="str">
+        <x:v>2102541149013708819</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="48" customHeight="1">
+      <x:c r="A75" s="9" t="str">
+        <x:v>X006</x:v>
+      </x:c>
+      <x:c r="B75" s="21" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C75" s="9" t="str">
+        <x:v>1Broom (@The1Broom)</x:v>
+      </x:c>
+      <x:c r="D75" s="9" t="str">
+        <x:v>질문</x:v>
+      </x:c>
+      <x:c r="E75" s="9" t="str">
+        <x:v>게임 기획·개발 범위 조절</x:v>
+      </x:c>
+      <x:c r="F75" s="10" t="str">
+        <x:v>게임 기획·개발 범위 조절</x:v>
+      </x:c>
+      <x:c r="G75" s="10" t="str">
+        <x:v>Congrats on 5K. Question: what's one feature you cut from the game that you still secretly miss?</x:v>
+      </x:c>
+      <x:c r="H75" s="9" t="str">
+        <x:v>Sep 22</x:v>
+      </x:c>
+      <x:c r="I75" s="9" t="d">
+        <x:v>2026-09-22T23:21:33.000Z</x:v>
+      </x:c>
+      <x:c r="J75" s="9" t="e">
+        <x:f>HYPERLINK("captures/x/X006.png","이미지 열기")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=captures/x/X006.png, friendlyName=이미지 열기</x:v>
+      </x:c>
+      <x:c r="K75" s="9" t="e">
+        <x:f>HYPERLINK("https://x.com/The1Broom/status/2102538824442114219","원문 열기")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://x.com/The1Broom/status/2102538824442114219, friendlyName=원문 열기</x:v>
+      </x:c>
+      <x:c r="L75" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M75" s="9" t="str">
+        <x:v>2102538824442114219</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R562373dfbb254237"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ed8677ccdc74ce5"/>
   </x:tableParts>
 </x:worksheet>
 </file>